--- a/Excel_files/susswein2025.xlsx
+++ b/Excel_files/susswein2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\udickman\pySNNAP\Excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0544A87-A7D1-4BC7-9ABA-806CF0E1D7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08581A00-2276-4EBA-9190-CFB48E0AB9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="874" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="874" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="3" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2285" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2286" uniqueCount="233">
   <si>
     <t>Name</t>
   </si>
@@ -4191,7 +4191,9 @@
     <col min="87" max="87" width="4.26953125" style="14" customWidth="1"/>
     <col min="88" max="94" width="3.54296875" style="14" customWidth="1"/>
     <col min="95" max="95" width="5.1796875" style="14" customWidth="1"/>
-    <col min="96" max="103" width="3.26953125" style="14" customWidth="1"/>
+    <col min="96" max="99" width="3.26953125" style="14" customWidth="1"/>
+    <col min="100" max="100" width="5.08984375" style="14" customWidth="1"/>
+    <col min="101" max="103" width="3.26953125" style="14" customWidth="1"/>
     <col min="104" max="104" width="7.81640625" style="14" customWidth="1"/>
     <col min="105" max="106" width="3.81640625" style="14" customWidth="1"/>
     <col min="107" max="114" width="2.26953125" style="14" customWidth="1"/>
@@ -14714,13 +14716,13 @@
         <v>176</v>
       </c>
       <c r="C19" s="62">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D19" s="62">
         <v>60</v>
       </c>
       <c r="E19" s="62">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="G19" s="62"/>
       <c r="H19" s="62"/>
@@ -14730,10 +14732,18 @@
       <c r="M19" s="14"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B20" s="41"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
+      <c r="B20" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="62">
+        <v>0.5</v>
+      </c>
+      <c r="D20" s="62">
+        <v>60</v>
+      </c>
+      <c r="E20" s="62">
+        <v>20</v>
+      </c>
       <c r="G20" s="62"/>
       <c r="H20" s="62"/>
       <c r="I20" s="62"/>
